--- a/output/第10期計画_認定率の年齢調整分析.xlsx
+++ b/output/第10期計画_認定率の年齢調整分析.xlsx
@@ -1025,10 +1025,10 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="72" customHeight="1">
+    <row r="22" ht="108" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>注1）65〜74歳及び75〜84歳の認定率は、B4系列に直接の出力がないため逆算した。75歳以上人口＝75歳以上認定者数÷75歳以上認定率、65〜74歳人口＝第1号被保険者数－75歳以上人口、65〜74歳認定者数＝合計認定者数－75歳以上認定者数として算定している。認定率は小数第1位までの公表値であるため、逆算した人口には丸め誤差が含まれる。注2）B5・B6の「調整済み」は見える化システムが年齢構成を調整した値である。2系列あり、【他地域と比較】は全国の年齢構成、【注目する地域のみ】は当該地域の基準年の年齢構成を基準とする。本分析は他地域との比較に用いる前者を主とする。注3）B5・B6は令和7年3月末（令和6年度末）までであり、令和8年3月末の値はない。</t>
+          <t>注1）65〜74歳及び75〜84歳の認定率は、B4系列に直接の出力がないため逆算した。75歳以上人口＝75歳以上認定者数÷75歳以上認定率、65〜74歳人口＝第1号被保険者数－75歳以上人口、65〜74歳認定者数＝合計認定者数－75歳以上認定者数として算定している。認定率は小数第1位までの公表値であるため、逆算した人口には丸め誤差が含まれる。注2）B5・B6の「調整済み」は見える化システムが年齢構成を調整した値である。2系列あり、【他地域と比較】は全国の年齢構成、【注目する地域のみ】は当該地域の基準年の年齢構成を基準とするという見立てによっているが、**この見立ては原典で確かめられていない**（確認事項No.190）。令和8年10月19日に受領した【注目する地域のみ】の出力により、当広域連合の値は後者の側であることが確かめられた（平成25年3月末から令和7年3月末までの221件が受領値と一致）。本分析は他地域との比較に用いるものとして前者を主としているが、**2系列の値を混ぜて1つの文に並べない。**1つの系列の中での時点の比較は標準化の基準によらず成り立つ。注3）**令和8年3月末の値は【注目する地域のみ】のみ受領している**（令和8年10月19日）。【他地域と比較】は令和7年3月末までである。</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2291,7 +2291,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>見える化システムのB5a系列は、年齢構成を調整した認定率を要介護度別に出力する。2系列あり、【他地域と比較】は全国の年齢構成、【注目する地域のみ】は当該地域の基準年の年齢構成を基準とする。他団体との比較に用いるのは前者である。</t>
+          <t>見える化システムのB5a系列は、年齢構成を調整した認定率を要介護度別に出力する。2系列あり、【他地域と比較】は全国の年齢構成、【注目する地域のみ】は当該地域の基準年の年齢構成を基準とするという見立てによるが、原典で確かめられていない（確認事項No.190）。当広域連合の値が後者の側であることは令和8年10月19日に受領した出力により確かめられた。</t>
         </is>
       </c>
     </row>
@@ -2950,6 +2950,9 @@
         <v>2.9</v>
       </c>
       <c r="O18" s="11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P18" s="8" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -2999,6 +3002,9 @@
         <v>2.8</v>
       </c>
       <c r="O19" s="11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P19" s="8" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -3048,7 +3054,10 @@
         <v>4.6</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>0.1</v>
+        <v>4.8</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -3097,7 +3106,10 @@
         <v>2.9</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>-0.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -3146,6 +3158,9 @@
         <v>1.9</v>
       </c>
       <c r="O22" s="11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P22" s="8" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -3194,8 +3209,11 @@
       <c r="N23" s="8" t="n">
         <v>1.8</v>
       </c>
-      <c r="O23" s="11" t="n">
-        <v>-0.1</v>
+      <c r="O23" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -3244,7 +3262,10 @@
         <v>1.5</v>
       </c>
       <c r="O24" s="11" t="n">
-        <v>-0.3</v>
+        <v>1.4</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -3293,6 +3314,9 @@
         <v>18.4</v>
       </c>
       <c r="O25" s="14" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="P25" s="13" t="n">
         <v>-1.3</v>
       </c>
     </row>
@@ -3370,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3636,9 +3660,12 @@
         <v>5.3</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>-0.7</v>
+        <v>5.2</v>
       </c>
       <c r="P7" s="8" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q7" s="8" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -3688,10 +3715,13 @@
         <v>13.2</v>
       </c>
       <c r="O8" s="10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="P8" s="8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="P8" s="8" t="n">
-        <v>0.4</v>
+      <c r="Q8" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
